--- a/Fruto - Maturação Fieldspec/analise_completa_resultados_cv.xlsx
+++ b/Fruto - Maturação Fieldspec/analise_completa_resultados_cv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dry_2\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C0001E9-79E5-40D3-950D-E995203E2713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DFA7FF3-A1E4-4C68-A026-57703C1ED7FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20508" yWindow="960" windowWidth="20616" windowHeight="11016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1835" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1931" uniqueCount="174">
   <si>
     <t>Atributo</t>
   </si>
@@ -952,7 +952,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K305"/>
+  <dimension ref="A1:K321"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.88671875" bestFit="1" customWidth="1"/>
@@ -964,7 +964,7 @@
     <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.44140625" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5546875" customWidth="1"/>
+    <col min="11" max="11" width="129.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -11642,6 +11642,566 @@
         <v>77</v>
       </c>
     </row>
+    <row r="306" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A306" t="s">
+        <v>163</v>
+      </c>
+      <c r="B306" t="s">
+        <v>20</v>
+      </c>
+      <c r="C306" t="s">
+        <v>73</v>
+      </c>
+      <c r="D306" t="s">
+        <v>18</v>
+      </c>
+      <c r="E306">
+        <v>0.76512055076421426</v>
+      </c>
+      <c r="F306">
+        <v>0.1160439015224214</v>
+      </c>
+      <c r="G306">
+        <v>19.108498236176779</v>
+      </c>
+      <c r="H306">
+        <v>0.76512055076421426</v>
+      </c>
+      <c r="I306" t="s">
+        <v>43</v>
+      </c>
+      <c r="J306">
+        <v>2.578522920608521</v>
+      </c>
+      <c r="K306" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="307" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A307" t="s">
+        <v>163</v>
+      </c>
+      <c r="B307" t="s">
+        <v>20</v>
+      </c>
+      <c r="C307" t="s">
+        <v>32</v>
+      </c>
+      <c r="D307" t="s">
+        <v>18</v>
+      </c>
+      <c r="E307">
+        <v>0.72857131885112036</v>
+      </c>
+      <c r="F307">
+        <v>0.16507583950005039</v>
+      </c>
+      <c r="G307">
+        <v>20.34707820037664</v>
+      </c>
+      <c r="H307">
+        <v>0.72857131885112036</v>
+      </c>
+      <c r="I307" t="s">
+        <v>43</v>
+      </c>
+      <c r="J307">
+        <v>2.6959924697875981</v>
+      </c>
+      <c r="K307" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="308" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A308" t="s">
+        <v>163</v>
+      </c>
+      <c r="B308" t="s">
+        <v>20</v>
+      </c>
+      <c r="C308" t="s">
+        <v>21</v>
+      </c>
+      <c r="D308" t="s">
+        <v>14</v>
+      </c>
+      <c r="E308">
+        <v>0.72812614598017544</v>
+      </c>
+      <c r="F308">
+        <v>0.13708758518541869</v>
+      </c>
+      <c r="G308">
+        <v>20.560996274550352</v>
+      </c>
+      <c r="H308">
+        <v>0.72812614598017544</v>
+      </c>
+      <c r="I308" t="s">
+        <v>36</v>
+      </c>
+      <c r="J308">
+        <v>3.38741135597229</v>
+      </c>
+      <c r="K308" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="309" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A309" t="s">
+        <v>163</v>
+      </c>
+      <c r="B309" t="s">
+        <v>20</v>
+      </c>
+      <c r="C309" t="s">
+        <v>46</v>
+      </c>
+      <c r="D309" t="s">
+        <v>14</v>
+      </c>
+      <c r="E309">
+        <v>0.69737234255498892</v>
+      </c>
+      <c r="F309">
+        <v>0.1378557143134656</v>
+      </c>
+      <c r="G309">
+        <v>21.479607619332398</v>
+      </c>
+      <c r="H309">
+        <v>0.69737234255498892</v>
+      </c>
+      <c r="I309" t="s">
+        <v>22</v>
+      </c>
+      <c r="J309">
+        <v>14.303698778152469</v>
+      </c>
+      <c r="K309" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="310" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A310" t="s">
+        <v>163</v>
+      </c>
+      <c r="B310" t="s">
+        <v>20</v>
+      </c>
+      <c r="C310" t="s">
+        <v>45</v>
+      </c>
+      <c r="D310" t="s">
+        <v>14</v>
+      </c>
+      <c r="E310">
+        <v>0.69588630899036419</v>
+      </c>
+      <c r="F310">
+        <v>0.1386915547435954</v>
+      </c>
+      <c r="G310">
+        <v>21.52922506523738</v>
+      </c>
+      <c r="H310">
+        <v>0.69588630899036419</v>
+      </c>
+      <c r="I310" t="s">
+        <v>22</v>
+      </c>
+      <c r="J310">
+        <v>2.816990852355957</v>
+      </c>
+      <c r="K310" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="311" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A311" t="s">
+        <v>163</v>
+      </c>
+      <c r="B311" t="s">
+        <v>20</v>
+      </c>
+      <c r="C311" t="s">
+        <v>56</v>
+      </c>
+      <c r="D311" t="s">
+        <v>14</v>
+      </c>
+      <c r="E311">
+        <v>0.68060165197006339</v>
+      </c>
+      <c r="F311">
+        <v>0.13929181201452359</v>
+      </c>
+      <c r="G311">
+        <v>21.914777218405082</v>
+      </c>
+      <c r="H311">
+        <v>0.68060165197006339</v>
+      </c>
+      <c r="I311" t="s">
+        <v>22</v>
+      </c>
+      <c r="J311">
+        <v>3.2044146060943599</v>
+      </c>
+      <c r="K311" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="312" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A312" t="s">
+        <v>163</v>
+      </c>
+      <c r="B312" t="s">
+        <v>20</v>
+      </c>
+      <c r="C312" t="s">
+        <v>41</v>
+      </c>
+      <c r="D312" t="s">
+        <v>14</v>
+      </c>
+      <c r="E312">
+        <v>0.65408282256998695</v>
+      </c>
+      <c r="F312">
+        <v>0.15043414692981399</v>
+      </c>
+      <c r="G312">
+        <v>23.069886273471742</v>
+      </c>
+      <c r="H312">
+        <v>0.65408282256998695</v>
+      </c>
+      <c r="I312" t="s">
+        <v>36</v>
+      </c>
+      <c r="J312">
+        <v>2.597725629806519</v>
+      </c>
+      <c r="K312" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="313" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A313" t="s">
+        <v>163</v>
+      </c>
+      <c r="B313" t="s">
+        <v>20</v>
+      </c>
+      <c r="C313" t="s">
+        <v>35</v>
+      </c>
+      <c r="D313" t="s">
+        <v>14</v>
+      </c>
+      <c r="E313">
+        <v>0.63793348233706304</v>
+      </c>
+      <c r="F313">
+        <v>0.1409490645965312</v>
+      </c>
+      <c r="G313">
+        <v>23.709954714068509</v>
+      </c>
+      <c r="H313">
+        <v>0.63793348233706304</v>
+      </c>
+      <c r="I313" t="s">
+        <v>22</v>
+      </c>
+      <c r="J313">
+        <v>2.681422233581543</v>
+      </c>
+      <c r="K313" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="314" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A314" t="s">
+        <v>163</v>
+      </c>
+      <c r="B314" t="s">
+        <v>20</v>
+      </c>
+      <c r="C314" t="s">
+        <v>38</v>
+      </c>
+      <c r="D314" t="s">
+        <v>14</v>
+      </c>
+      <c r="E314">
+        <v>0.63793348233684899</v>
+      </c>
+      <c r="F314">
+        <v>0.14094906459569831</v>
+      </c>
+      <c r="G314">
+        <v>23.7099547141041</v>
+      </c>
+      <c r="H314">
+        <v>0.63793348233684899</v>
+      </c>
+      <c r="I314" t="s">
+        <v>22</v>
+      </c>
+      <c r="J314">
+        <v>2.6987788677215581</v>
+      </c>
+      <c r="K314" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="315" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A315" t="s">
+        <v>163</v>
+      </c>
+      <c r="B315" t="s">
+        <v>20</v>
+      </c>
+      <c r="C315" t="s">
+        <v>13</v>
+      </c>
+      <c r="D315" t="s">
+        <v>14</v>
+      </c>
+      <c r="E315">
+        <v>0.63586133382822851</v>
+      </c>
+      <c r="F315">
+        <v>0.1267717382259389</v>
+      </c>
+      <c r="G315">
+        <v>24.12568093856607</v>
+      </c>
+      <c r="H315">
+        <v>0.63586133382822851</v>
+      </c>
+      <c r="I315" t="s">
+        <v>43</v>
+      </c>
+      <c r="J315">
+        <v>2.5866529941558838</v>
+      </c>
+      <c r="K315" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="316" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A316" t="s">
+        <v>163</v>
+      </c>
+      <c r="B316" t="s">
+        <v>20</v>
+      </c>
+      <c r="C316" t="s">
+        <v>24</v>
+      </c>
+      <c r="D316" t="s">
+        <v>18</v>
+      </c>
+      <c r="E316">
+        <v>0.63563784729004069</v>
+      </c>
+      <c r="F316">
+        <v>0.25901055135488399</v>
+      </c>
+      <c r="G316">
+        <v>23.2019970596739</v>
+      </c>
+      <c r="H316">
+        <v>0.63563784729004069</v>
+      </c>
+      <c r="I316" t="s">
+        <v>65</v>
+      </c>
+      <c r="J316">
+        <v>2.5845015048980708</v>
+      </c>
+      <c r="K316" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="317" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A317" t="s">
+        <v>163</v>
+      </c>
+      <c r="B317" t="s">
+        <v>20</v>
+      </c>
+      <c r="C317" t="s">
+        <v>49</v>
+      </c>
+      <c r="D317" t="s">
+        <v>14</v>
+      </c>
+      <c r="E317">
+        <v>0.62651588059110974</v>
+      </c>
+      <c r="F317">
+        <v>0.12933118214916961</v>
+      </c>
+      <c r="G317">
+        <v>24.141744664238551</v>
+      </c>
+      <c r="H317">
+        <v>0.62651588059110974</v>
+      </c>
+      <c r="I317" t="s">
+        <v>22</v>
+      </c>
+      <c r="J317">
+        <v>2.603460311889648</v>
+      </c>
+      <c r="K317" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="318" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A318" t="s">
+        <v>163</v>
+      </c>
+      <c r="B318" t="s">
+        <v>20</v>
+      </c>
+      <c r="C318" t="s">
+        <v>19</v>
+      </c>
+      <c r="D318" t="s">
+        <v>14</v>
+      </c>
+      <c r="E318">
+        <v>0.56369404074513485</v>
+      </c>
+      <c r="F318">
+        <v>0.20398983964860001</v>
+      </c>
+      <c r="G318">
+        <v>25.949964742090209</v>
+      </c>
+      <c r="H318">
+        <v>0.56369404074513485</v>
+      </c>
+      <c r="I318" t="s">
+        <v>65</v>
+      </c>
+      <c r="J318">
+        <v>2.603861808776855</v>
+      </c>
+      <c r="K318" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="319" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A319" t="s">
+        <v>163</v>
+      </c>
+      <c r="B319" t="s">
+        <v>20</v>
+      </c>
+      <c r="C319" t="s">
+        <v>17</v>
+      </c>
+      <c r="D319" t="s">
+        <v>18</v>
+      </c>
+      <c r="E319">
+        <v>0.5377870221712675</v>
+      </c>
+      <c r="F319">
+        <v>0.2077471143665604</v>
+      </c>
+      <c r="G319">
+        <v>26.634647665392581</v>
+      </c>
+      <c r="H319">
+        <v>0.5377870221712675</v>
+      </c>
+      <c r="I319" t="s">
+        <v>43</v>
+      </c>
+      <c r="J319">
+        <v>2.5726056098937988</v>
+      </c>
+      <c r="K319" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="320" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A320" t="s">
+        <v>163</v>
+      </c>
+      <c r="B320" t="s">
+        <v>20</v>
+      </c>
+      <c r="C320" t="s">
+        <v>42</v>
+      </c>
+      <c r="D320" t="s">
+        <v>18</v>
+      </c>
+      <c r="E320">
+        <v>0.53392526767259463</v>
+      </c>
+      <c r="F320">
+        <v>0.33301023183638617</v>
+      </c>
+      <c r="G320">
+        <v>26.428411099153621</v>
+      </c>
+      <c r="H320">
+        <v>0.53392526767259463</v>
+      </c>
+      <c r="I320" t="s">
+        <v>43</v>
+      </c>
+      <c r="J320">
+        <v>2.578339576721191</v>
+      </c>
+      <c r="K320" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="321" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A321" t="s">
+        <v>163</v>
+      </c>
+      <c r="B321" t="s">
+        <v>20</v>
+      </c>
+      <c r="C321" t="s">
+        <v>50</v>
+      </c>
+      <c r="D321" t="s">
+        <v>18</v>
+      </c>
+      <c r="E321">
+        <v>0.52093282652949335</v>
+      </c>
+      <c r="F321">
+        <v>0.34042639148556081</v>
+      </c>
+      <c r="G321">
+        <v>26.82111233900287</v>
+      </c>
+      <c r="H321">
+        <v>0.52093282652949335</v>
+      </c>
+      <c r="I321" t="s">
+        <v>43</v>
+      </c>
+      <c r="J321">
+        <v>2.5269038677215581</v>
+      </c>
+      <c r="K321" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
